--- a/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N8_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T1995_W0021F0001T0006Z000C1N8_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>26.66865850848199</v>
+        <v>4.333657007628323</v>
       </c>
       <c r="D2" t="n">
-        <v>26.68358478566198</v>
+        <v>4.336082527670072</v>
       </c>
       <c r="E2" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F2" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>22.43508317341268</v>
+        <v>3.645701015679561</v>
       </c>
       <c r="D3" t="n">
-        <v>26.47983322420663</v>
+        <v>4.302972898933577</v>
       </c>
       <c r="E3" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F3" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>22.2892911506849</v>
+        <v>3.622009811986296</v>
       </c>
       <c r="D4" t="n">
-        <v>29.24541611933459</v>
+        <v>4.75238011939187</v>
       </c>
       <c r="E4" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F4" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>4.026655902782387</v>
+        <v>0.654331584202138</v>
       </c>
       <c r="D5" t="n">
-        <v>14.43321995160604</v>
+        <v>2.345398242135981</v>
       </c>
       <c r="E5" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F5" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>20.7430382702025</v>
+        <v>3.370743718907907</v>
       </c>
       <c r="D6" t="n">
-        <v>29.14105589820624</v>
+        <v>4.735421583458514</v>
       </c>
       <c r="E6" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F6" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>28.50415980257353</v>
+        <v>4.631925967918198</v>
       </c>
       <c r="D7" t="n">
-        <v>29.41759411173427</v>
+        <v>4.780359043156819</v>
       </c>
       <c r="E7" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F7" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.61319946597012</v>
+        <v>3.512144913220145</v>
       </c>
       <c r="D8" t="n">
-        <v>21.77199023773921</v>
+        <v>3.537948413632622</v>
       </c>
       <c r="E8" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F8" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>20.40666434302753</v>
+        <v>3.316082955741973</v>
       </c>
       <c r="D9" t="n">
-        <v>21.24719097627563</v>
+        <v>3.45266853364479</v>
       </c>
       <c r="E9" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F9" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.5183566836634</v>
+        <v>3.334232961095303</v>
       </c>
       <c r="D10" t="n">
-        <v>20.74658193340951</v>
+        <v>3.371319564179045</v>
       </c>
       <c r="E10" t="n">
-        <v>6.505812437782394</v>
+        <v>1.057194521139639</v>
       </c>
       <c r="F10" t="n">
-        <v>4.832555219321797</v>
+        <v>0.7852902231397919</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
